--- a/3.1.4-素材/智能健康监测系统数据集.xlsx
+++ b/3.1.4-素材/智能健康监测系统数据集.xlsx
@@ -1,25 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI课程\新题目\给刘老师参考0705\20240903\04-题库资源（人工智能训练师）（9.15新版本）\04-题库资源\人工智能训练师_3级_20240915\人工智能训练师_3级_操作技能试题（题库）\3.1.4\3.1.4-素材\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gqq/OpenSource/ai-training/3.1.4-素材/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C048A64-89C4-AF4F-AAED-B5CDC266E0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10300"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="18000" windowHeight="12340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$G$169</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="23" r:id="rId3"/>
+  </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="134">
   <si>
     <t>时间戳</t>
   </si>
@@ -400,17 +421,41 @@
   <si>
     <t>血糖</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOUR</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Average of 收缩压</t>
+  </si>
+  <si>
+    <t>Average of 舒张压</t>
+  </si>
+  <si>
+    <t>Average of 血糖</t>
+  </si>
+  <si>
+    <t>Average of 体脂分析</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -423,7 +468,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -449,18 +494,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -473,6 +519,1774 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gu QQ" refreshedDate="46310.616907407406" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="169" xr:uid="{BCB34E4A-A3C0-5648-9EFB-2A5433152708}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:G1048576" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="时间戳" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="收缩压" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="90" maxValue="150"/>
+    </cacheField>
+    <cacheField name="舒张压" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="60" maxValue="90"/>
+    </cacheField>
+    <cacheField name="血糖" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="4.0199999999999996" maxValue="7.75" count="70">
+        <m/>
+        <n v="4.37"/>
+        <n v="7.71"/>
+        <n v="6.46"/>
+        <n v="4.5999999999999996"/>
+        <n v="6.28"/>
+        <n v="5.31"/>
+        <n v="4.0599999999999996"/>
+        <n v="7.56"/>
+        <n v="6.2"/>
+        <n v="4.91"/>
+        <n v="4.0199999999999996"/>
+        <n v="7.75"/>
+        <n v="6.66"/>
+        <n v="4.21"/>
+        <n v="6.33"/>
+        <n v="5.37"/>
+        <n v="4.3"/>
+        <n v="6.94"/>
+        <n v="5.86"/>
+        <n v="4.49"/>
+        <n v="4.6100000000000003"/>
+        <n v="6.25"/>
+        <n v="5.58"/>
+        <n v="6.82"/>
+        <n v="6.57"/>
+        <n v="4.2"/>
+        <n v="6.93"/>
+        <n v="6.18"/>
+        <n v="4.25"/>
+        <n v="6.31"/>
+        <n v="5.13"/>
+        <n v="4.95"/>
+        <n v="7.74"/>
+        <n v="6.62"/>
+        <n v="6.37"/>
+        <n v="4.6399999999999997"/>
+        <n v="4.12"/>
+        <n v="6.89"/>
+        <n v="5.07"/>
+        <n v="6.47"/>
+        <n v="4.3099999999999996"/>
+        <n v="6.09"/>
+        <n v="4.38"/>
+        <n v="4.97"/>
+        <n v="7.4"/>
+        <n v="6.88"/>
+        <n v="4.8899999999999997"/>
+        <n v="7.08"/>
+        <n v="6.84"/>
+        <n v="4.09"/>
+        <n v="6.35"/>
+        <n v="5.09"/>
+        <n v="4.53"/>
+        <n v="4.3899999999999997"/>
+        <n v="6.49"/>
+        <n v="4.3600000000000003"/>
+        <n v="6.51"/>
+        <n v="4.1399999999999997"/>
+        <n v="7.44"/>
+        <n v="5.15"/>
+        <n v="5.19"/>
+        <n v="4.7699999999999996"/>
+        <n v="6.36"/>
+        <n v="5.01"/>
+        <n v="4.82"/>
+        <n v="7.27"/>
+        <n v="6.13"/>
+        <n v="5.72"/>
+        <n v="4.32"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="体脂分析" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.17" maxValue="0.17"/>
+    </cacheField>
+    <cacheField name="响应时间" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.2" maxValue="0.99"/>
+    </cacheField>
+    <cacheField name="HOUR" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="22" count="15">
+        <n v="0"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="9"/>
+        <n v="10"/>
+        <n v="12"/>
+        <n v="13"/>
+        <n v="14"/>
+        <n v="16"/>
+        <n v="18"/>
+        <n v="19"/>
+        <n v="20"/>
+        <n v="22"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="169">
+  <r>
+    <s v="2024-09-15 00:00"/>
+    <n v="111"/>
+    <n v="80"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.8"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="2024-09-15 06:00"/>
+    <n v="128"/>
+    <n v="79"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.5"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="2024-09-15 07:00"/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <m/>
+    <n v="0.89"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-15 07:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <n v="0.17"/>
+    <n v="0.69"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-15 07:30"/>
+    <n v="128"/>
+    <n v="74"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.56999999999999995"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-15 08:00"/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <m/>
+    <n v="0.74"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="2024-09-15 09:00"/>
+    <m/>
+    <m/>
+    <x v="3"/>
+    <m/>
+    <n v="0.7"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="2024-09-15 10:00"/>
+    <n v="132"/>
+    <n v="67"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.78"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <s v="2024-09-15 12:00"/>
+    <m/>
+    <m/>
+    <x v="4"/>
+    <m/>
+    <n v="0.47"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-15 12:00"/>
+    <n v="110"/>
+    <n v="66"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.99"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-15 13:00"/>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <n v="0.51"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-15 13:00"/>
+    <n v="108"/>
+    <n v="82"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.99"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-15 14:00"/>
+    <m/>
+    <m/>
+    <x v="6"/>
+    <m/>
+    <n v="0.41"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <s v="2024-09-15 16:00"/>
+    <n v="100"/>
+    <n v="70"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.95"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <s v="2024-09-15 18:00"/>
+    <m/>
+    <m/>
+    <x v="7"/>
+    <m/>
+    <n v="0.97"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-15 18:00"/>
+    <n v="113"/>
+    <n v="80"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.51"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-15 19:00"/>
+    <m/>
+    <m/>
+    <x v="8"/>
+    <m/>
+    <n v="0.54"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-15 19:00"/>
+    <n v="125"/>
+    <n v="67"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.39"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-15 20:00"/>
+    <m/>
+    <m/>
+    <x v="9"/>
+    <m/>
+    <n v="0.66"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <s v="2024-09-15 22:00"/>
+    <m/>
+    <m/>
+    <x v="10"/>
+    <m/>
+    <n v="0.66"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-15 22:00"/>
+    <n v="113"/>
+    <n v="62"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.87"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-16 00:00"/>
+    <n v="105"/>
+    <n v="74"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.28000000000000003"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="2024-09-16 06:00"/>
+    <n v="91"/>
+    <n v="83"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.37"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="2024-09-16 07:00"/>
+    <m/>
+    <m/>
+    <x v="11"/>
+    <m/>
+    <n v="0.8"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-16 07:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <n v="0.17"/>
+    <n v="0.65"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-16 07:30"/>
+    <n v="143"/>
+    <n v="89"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.23"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-16 08:00"/>
+    <m/>
+    <m/>
+    <x v="12"/>
+    <m/>
+    <n v="0.86"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="2024-09-16 09:00"/>
+    <m/>
+    <m/>
+    <x v="13"/>
+    <m/>
+    <n v="0.51"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="2024-09-16 10:00"/>
+    <n v="127"/>
+    <n v="61"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.56000000000000005"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <s v="2024-09-16 12:00"/>
+    <m/>
+    <m/>
+    <x v="14"/>
+    <m/>
+    <n v="0.27"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-16 12:00"/>
+    <n v="110"/>
+    <n v="60"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.78"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-16 13:00"/>
+    <m/>
+    <m/>
+    <x v="15"/>
+    <m/>
+    <n v="0.27"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-16 13:00"/>
+    <n v="101"/>
+    <n v="85"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.8"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-16 14:00"/>
+    <m/>
+    <m/>
+    <x v="16"/>
+    <m/>
+    <n v="0.37"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <s v="2024-09-16 16:00"/>
+    <n v="111"/>
+    <n v="88"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.33"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <s v="2024-09-16 18:00"/>
+    <m/>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <n v="0.64"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-16 18:00"/>
+    <n v="133"/>
+    <n v="84"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.85"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-16 19:00"/>
+    <m/>
+    <m/>
+    <x v="18"/>
+    <m/>
+    <n v="0.28000000000000003"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-16 19:00"/>
+    <n v="138"/>
+    <n v="86"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.94"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-16 20:00"/>
+    <m/>
+    <m/>
+    <x v="19"/>
+    <m/>
+    <n v="0.32"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <s v="2024-09-16 22:00"/>
+    <m/>
+    <m/>
+    <x v="20"/>
+    <m/>
+    <n v="0.67"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-16 22:00"/>
+    <n v="131"/>
+    <n v="87"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.88"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-17 00:00"/>
+    <n v="91"/>
+    <n v="79"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.41"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="2024-09-17 06:00"/>
+    <n v="136"/>
+    <n v="89"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.65"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="2024-09-17 07:00"/>
+    <m/>
+    <m/>
+    <x v="21"/>
+    <m/>
+    <n v="0.59"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-17 07:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <n v="0.17"/>
+    <n v="0.68"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-17 07:30"/>
+    <n v="150"/>
+    <n v="71"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.6"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-17 08:00"/>
+    <m/>
+    <m/>
+    <x v="22"/>
+    <m/>
+    <n v="0.76"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="2024-09-17 09:00"/>
+    <m/>
+    <m/>
+    <x v="23"/>
+    <m/>
+    <n v="0.46"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="2024-09-17 10:00"/>
+    <n v="92"/>
+    <n v="64"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.61"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <s v="2024-09-17 12:00"/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <m/>
+    <n v="0.52"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-17 12:00"/>
+    <n v="140"/>
+    <n v="66"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.53"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-17 13:00"/>
+    <m/>
+    <m/>
+    <x v="24"/>
+    <m/>
+    <n v="0.79"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-17 13:00"/>
+    <n v="110"/>
+    <n v="68"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.44"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-17 14:00"/>
+    <m/>
+    <m/>
+    <x v="25"/>
+    <m/>
+    <n v="0.8"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <s v="2024-09-17 16:00"/>
+    <n v="128"/>
+    <n v="77"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.45"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <s v="2024-09-17 18:00"/>
+    <m/>
+    <m/>
+    <x v="26"/>
+    <m/>
+    <n v="0.62"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-17 18:00"/>
+    <n v="93"/>
+    <n v="84"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.61"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-17 19:00"/>
+    <m/>
+    <m/>
+    <x v="27"/>
+    <m/>
+    <n v="0.94"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-17 19:00"/>
+    <n v="103"/>
+    <n v="77"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.65"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-17 20:00"/>
+    <m/>
+    <m/>
+    <x v="28"/>
+    <m/>
+    <n v="0.76"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <s v="2024-09-17 22:00"/>
+    <m/>
+    <m/>
+    <x v="29"/>
+    <m/>
+    <n v="0.51"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-17 22:00"/>
+    <n v="98"/>
+    <n v="85"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.4"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-18 00:00"/>
+    <n v="118"/>
+    <n v="90"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.62"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="2024-09-18 06:00"/>
+    <n v="117"/>
+    <n v="74"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.53"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="2024-09-18 07:00"/>
+    <m/>
+    <m/>
+    <x v="21"/>
+    <m/>
+    <n v="0.42"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-18 07:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <n v="0.17"/>
+    <n v="0.64"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-18 07:30"/>
+    <n v="106"/>
+    <n v="71"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.62"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-18 08:00"/>
+    <m/>
+    <m/>
+    <x v="30"/>
+    <m/>
+    <n v="0.48"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="2024-09-18 09:00"/>
+    <m/>
+    <m/>
+    <x v="31"/>
+    <m/>
+    <n v="0.98"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="2024-09-18 10:00"/>
+    <n v="97"/>
+    <n v="74"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.64"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <s v="2024-09-18 12:00"/>
+    <m/>
+    <m/>
+    <x v="32"/>
+    <m/>
+    <n v="0.63"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-18 12:00"/>
+    <n v="124"/>
+    <n v="73"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.49"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-18 13:00"/>
+    <m/>
+    <m/>
+    <x v="33"/>
+    <m/>
+    <n v="0.69"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-18 13:00"/>
+    <n v="106"/>
+    <n v="63"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.71"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-18 14:00"/>
+    <m/>
+    <m/>
+    <x v="34"/>
+    <m/>
+    <n v="0.95"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <s v="2024-09-18 16:00"/>
+    <n v="139"/>
+    <n v="67"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.89"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <s v="2024-09-18 18:00"/>
+    <m/>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <n v="0.22"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-18 18:00"/>
+    <n v="93"/>
+    <n v="61"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.77"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-18 19:00"/>
+    <m/>
+    <m/>
+    <x v="28"/>
+    <m/>
+    <n v="0.8"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-18 19:00"/>
+    <n v="95"/>
+    <n v="81"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.95"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-18 20:00"/>
+    <m/>
+    <m/>
+    <x v="35"/>
+    <m/>
+    <n v="0.23"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <s v="2024-09-18 22:00"/>
+    <m/>
+    <m/>
+    <x v="36"/>
+    <m/>
+    <n v="0.63"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-18 22:00"/>
+    <n v="131"/>
+    <n v="63"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.73"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-19 00:00"/>
+    <n v="107"/>
+    <n v="74"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.63"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="2024-09-19 06:00"/>
+    <n v="107"/>
+    <n v="85"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.92"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="2024-09-19 07:00"/>
+    <m/>
+    <m/>
+    <x v="37"/>
+    <m/>
+    <n v="0.78"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-19 07:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <n v="0.17"/>
+    <n v="0.66"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-19 07:30"/>
+    <n v="143"/>
+    <n v="61"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.82"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-19 08:00"/>
+    <m/>
+    <m/>
+    <x v="38"/>
+    <m/>
+    <n v="0.39"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="2024-09-19 09:00"/>
+    <m/>
+    <m/>
+    <x v="39"/>
+    <m/>
+    <n v="0.69"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="2024-09-19 10:00"/>
+    <n v="99"/>
+    <n v="89"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.27"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <s v="2024-09-19 12:00"/>
+    <m/>
+    <m/>
+    <x v="10"/>
+    <m/>
+    <n v="0.74"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-19 12:00"/>
+    <n v="125"/>
+    <n v="73"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.92"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-19 13:00"/>
+    <m/>
+    <m/>
+    <x v="40"/>
+    <m/>
+    <n v="0.82"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-19 13:00"/>
+    <n v="120"/>
+    <n v="75"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.21"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-19 14:00"/>
+    <m/>
+    <m/>
+    <x v="15"/>
+    <m/>
+    <n v="0.27"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <s v="2024-09-19 16:00"/>
+    <n v="104"/>
+    <n v="67"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <s v="2024-09-19 18:00"/>
+    <m/>
+    <m/>
+    <x v="41"/>
+    <m/>
+    <n v="0.76"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-19 18:00"/>
+    <n v="103"/>
+    <n v="82"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.64"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-19 19:00"/>
+    <m/>
+    <m/>
+    <x v="18"/>
+    <m/>
+    <n v="0.71"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-19 19:00"/>
+    <n v="129"/>
+    <n v="80"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.38"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-19 20:00"/>
+    <m/>
+    <m/>
+    <x v="42"/>
+    <m/>
+    <n v="0.93"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <s v="2024-09-19 22:00"/>
+    <m/>
+    <m/>
+    <x v="43"/>
+    <m/>
+    <n v="0.76"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-19 22:00"/>
+    <n v="105"/>
+    <n v="72"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.49"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-20 00:00"/>
+    <n v="100"/>
+    <n v="78"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.88"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="2024-09-20 06:00"/>
+    <n v="113"/>
+    <n v="85"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.92"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="2024-09-20 07:00"/>
+    <m/>
+    <m/>
+    <x v="44"/>
+    <m/>
+    <n v="0.56999999999999995"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-20 07:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <n v="0.17"/>
+    <n v="0.63"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-20 07:30"/>
+    <n v="124"/>
+    <n v="87"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.36"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-20 08:00"/>
+    <m/>
+    <m/>
+    <x v="45"/>
+    <m/>
+    <n v="0.59"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="2024-09-20 09:00"/>
+    <m/>
+    <m/>
+    <x v="46"/>
+    <m/>
+    <n v="0.76"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="2024-09-20 10:00"/>
+    <n v="134"/>
+    <n v="68"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.23"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <s v="2024-09-20 12:00"/>
+    <m/>
+    <m/>
+    <x v="47"/>
+    <m/>
+    <n v="0.76"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-20 12:00"/>
+    <n v="118"/>
+    <n v="74"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.57999999999999996"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-20 13:00"/>
+    <m/>
+    <m/>
+    <x v="48"/>
+    <m/>
+    <n v="0.48"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-20 13:00"/>
+    <n v="134"/>
+    <n v="60"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.8"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-20 14:00"/>
+    <m/>
+    <m/>
+    <x v="49"/>
+    <m/>
+    <n v="0.63"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <s v="2024-09-20 16:00"/>
+    <n v="114"/>
+    <n v="66"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.98"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <s v="2024-09-20 18:00"/>
+    <m/>
+    <m/>
+    <x v="50"/>
+    <m/>
+    <n v="0.3"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-20 18:00"/>
+    <n v="98"/>
+    <n v="83"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.35"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-20 19:00"/>
+    <m/>
+    <m/>
+    <x v="51"/>
+    <m/>
+    <n v="0.27"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-20 19:00"/>
+    <n v="90"/>
+    <n v="71"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.94"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-20 20:00"/>
+    <m/>
+    <m/>
+    <x v="52"/>
+    <m/>
+    <n v="0.8"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <s v="2024-09-20 22:00"/>
+    <m/>
+    <m/>
+    <x v="53"/>
+    <m/>
+    <n v="0.39"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-20 22:00"/>
+    <n v="97"/>
+    <n v="83"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.37"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-21 00:00"/>
+    <n v="137"/>
+    <n v="82"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.63"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="2024-09-21 06:00"/>
+    <n v="106"/>
+    <n v="67"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.69"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="2024-09-21 07:00"/>
+    <m/>
+    <m/>
+    <x v="54"/>
+    <m/>
+    <n v="0.78"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-21 07:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <n v="0.17"/>
+    <n v="0.68"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-21 07:30"/>
+    <n v="134"/>
+    <n v="62"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-21 08:00"/>
+    <m/>
+    <m/>
+    <x v="55"/>
+    <m/>
+    <n v="0.32"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="2024-09-21 09:00"/>
+    <m/>
+    <m/>
+    <x v="13"/>
+    <m/>
+    <n v="0.63"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="2024-09-21 10:00"/>
+    <n v="122"/>
+    <n v="86"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.26"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <s v="2024-09-21 12:00"/>
+    <m/>
+    <m/>
+    <x v="56"/>
+    <m/>
+    <n v="0.65"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-21 12:00"/>
+    <n v="94"/>
+    <n v="69"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.91"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-21 13:00"/>
+    <m/>
+    <m/>
+    <x v="57"/>
+    <m/>
+    <n v="0.57999999999999996"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-21 13:00"/>
+    <n v="128"/>
+    <n v="85"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.99"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-21 14:00"/>
+    <m/>
+    <m/>
+    <x v="42"/>
+    <m/>
+    <n v="0.57999999999999996"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <s v="2024-09-21 16:00"/>
+    <n v="130"/>
+    <n v="87"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.89"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <s v="2024-09-21 18:00"/>
+    <m/>
+    <m/>
+    <x v="58"/>
+    <m/>
+    <n v="0.65"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-21 18:00"/>
+    <n v="96"/>
+    <n v="68"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.82"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-21 19:00"/>
+    <m/>
+    <m/>
+    <x v="59"/>
+    <m/>
+    <n v="0.47"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-21 19:00"/>
+    <n v="97"/>
+    <n v="71"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.7"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-21 20:00"/>
+    <m/>
+    <m/>
+    <x v="60"/>
+    <m/>
+    <n v="0.4"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <s v="2024-09-21 22:00"/>
+    <m/>
+    <m/>
+    <x v="61"/>
+    <m/>
+    <n v="0.49"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-21 22:00"/>
+    <n v="123"/>
+    <n v="60"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.24"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-22 00:00"/>
+    <n v="115"/>
+    <n v="82"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.69"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="2024-09-22 06:00"/>
+    <n v="112"/>
+    <n v="89"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.46"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="2024-09-22 07:00"/>
+    <m/>
+    <m/>
+    <x v="62"/>
+    <m/>
+    <n v="0.88"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-22 07:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <n v="0.17"/>
+    <n v="0.66"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-22 07:30"/>
+    <n v="123"/>
+    <n v="64"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.4"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2024-09-22 08:00"/>
+    <m/>
+    <m/>
+    <x v="63"/>
+    <m/>
+    <n v="0.84"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="2024-09-22 09:00"/>
+    <m/>
+    <m/>
+    <x v="64"/>
+    <m/>
+    <n v="0.24"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="2024-09-22 10:00"/>
+    <n v="124"/>
+    <n v="71"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.54"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <s v="2024-09-22 12:00"/>
+    <m/>
+    <m/>
+    <x v="65"/>
+    <m/>
+    <n v="0.52"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-22 12:00"/>
+    <n v="129"/>
+    <n v="81"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.93"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <s v="2024-09-22 13:00"/>
+    <m/>
+    <m/>
+    <x v="66"/>
+    <m/>
+    <n v="0.85"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-22 13:00"/>
+    <n v="116"/>
+    <n v="62"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.71"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <s v="2024-09-22 14:00"/>
+    <m/>
+    <m/>
+    <x v="3"/>
+    <m/>
+    <n v="0.65"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <s v="2024-09-22 16:00"/>
+    <n v="90"/>
+    <n v="62"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.28999999999999998"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <s v="2024-09-22 18:00"/>
+    <m/>
+    <m/>
+    <x v="62"/>
+    <m/>
+    <n v="0.42"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-22 18:00"/>
+    <n v="126"/>
+    <n v="74"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.34"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <s v="2024-09-22 19:00"/>
+    <m/>
+    <m/>
+    <x v="67"/>
+    <m/>
+    <n v="0.54"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-22 19:00"/>
+    <n v="103"/>
+    <n v="62"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.69"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <s v="2024-09-22 20:00"/>
+    <m/>
+    <m/>
+    <x v="68"/>
+    <m/>
+    <n v="0.27"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <s v="2024-09-22 22:00"/>
+    <m/>
+    <m/>
+    <x v="69"/>
+    <m/>
+    <n v="0.46"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <s v="2024-09-22 22:00"/>
+    <n v="90"/>
+    <n v="64"/>
+    <x v="0"/>
+    <m/>
+    <n v="0.6"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="14"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74FE6B49-9139-AC4B-8414-ABF22EB013AC}" name="PivotTable6" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:E19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <dataFields count="4">
+    <dataField name="Average of 收缩压" fld="1" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="Average of 舒张压" fld="2" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="Average of 血糖" fld="3" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="Average of 体脂分析" fld="4" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -759,15 +2573,263 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F169"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB92E58-24E7-6848-9828-B9529E53A3DE}">
+  <dimension ref="A3:E19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.36328125" style="3" customWidth="1"/>
-    <col min="2" max="6" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4">
+        <v>110.5</v>
+      </c>
+      <c r="C4" s="4">
+        <v>79.875</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4">
+        <v>113.75</v>
+      </c>
+      <c r="C5" s="4">
+        <v>81.375</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4">
+        <v>131.375</v>
+      </c>
+      <c r="C6" s="4">
+        <v>72.375</v>
+      </c>
+      <c r="D6" s="4">
+        <v>4.4824999999999999</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.16999999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4">
+        <v>6.8949999999999996</v>
+      </c>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>9</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4">
+        <v>5.9312499999999995</v>
+      </c>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4">
+        <v>115.875</v>
+      </c>
+      <c r="C9" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>12</v>
+      </c>
+      <c r="B10" s="4">
+        <v>118.75</v>
+      </c>
+      <c r="C10" s="4">
+        <v>70.25</v>
+      </c>
+      <c r="D10" s="4">
+        <v>4.6387499999999999</v>
+      </c>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>13</v>
+      </c>
+      <c r="B11" s="4">
+        <v>115.375</v>
+      </c>
+      <c r="C11" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="D11" s="4">
+        <v>6.8125</v>
+      </c>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>14</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4">
+        <v>6.1987500000000013</v>
+      </c>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>16</v>
+      </c>
+      <c r="B13" s="4">
+        <v>114.5</v>
+      </c>
+      <c r="C13" s="4">
+        <v>73</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <v>18</v>
+      </c>
+      <c r="B14" s="4">
+        <v>106.875</v>
+      </c>
+      <c r="C14" s="4">
+        <v>77</v>
+      </c>
+      <c r="D14" s="4">
+        <v>4.2712500000000002</v>
+      </c>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>19</v>
+      </c>
+      <c r="B15" s="4">
+        <v>110</v>
+      </c>
+      <c r="C15" s="4">
+        <v>74.375</v>
+      </c>
+      <c r="D15" s="4">
+        <v>6.8087499999999999</v>
+      </c>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>20</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4">
+        <v>5.8325000000000005</v>
+      </c>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>22</v>
+      </c>
+      <c r="B17" s="4">
+        <v>111</v>
+      </c>
+      <c r="C17" s="4">
+        <v>72</v>
+      </c>
+      <c r="D17" s="4">
+        <v>4.5887500000000001</v>
+      </c>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="4">
+        <v>114.8</v>
+      </c>
+      <c r="C19" s="4">
+        <v>74.525000000000006</v>
+      </c>
+      <c r="D19" s="4">
+        <v>5.6459999999999981</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0.16999999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G169"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="6" width="8.6640625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -777,2106 +2839,2788 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="G1" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" hidden="1">
+      <c r="A2" t="s">
         <v>115</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>111</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2">
         <v>80</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="G2">
+        <f>HOUR(A2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" hidden="1">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>128</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>79</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="G3">
+        <f t="shared" ref="G3:G66" si="0">HOUR(A3)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4">
         <v>4.37</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4">
         <v>0.89</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" hidden="1">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <v>0.17</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5">
         <v>0.69</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" hidden="1">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>128</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6">
         <v>74</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6">
         <v>0.56999999999999995</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7">
         <v>7.71</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7">
         <v>0.74</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8">
         <v>6.46</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" hidden="1">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>132</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9">
         <v>67</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9">
         <v>0.78</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10">
         <v>0.47</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" hidden="1">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>110</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11">
         <v>66</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12">
         <v>6.28</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" hidden="1">
+      <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <v>108</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13">
         <v>82</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14">
         <v>5.31</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14">
         <v>0.41</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" hidden="1">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15">
         <v>100</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15">
         <v>70</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16">
         <v>4.0599999999999996</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16">
         <v>0.97</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" hidden="1">
+      <c r="A17" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17">
         <v>113</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17">
         <v>80</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18">
         <v>7.56</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18">
         <v>0.54</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" hidden="1">
+      <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <v>125</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19">
         <v>67</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19">
         <v>0.39</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20">
         <v>6.2</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20">
         <v>0.66</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21">
         <v>4.91</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21">
         <v>0.66</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" hidden="1">
+      <c r="A22" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22">
         <v>113</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22">
         <v>62</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22">
         <v>0.87</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" hidden="1">
+      <c r="A23" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23">
         <v>105</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23">
         <v>74</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23">
         <v>0.28000000000000003</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1">
+      <c r="A24" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24">
         <v>91</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24">
         <v>83</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24">
         <v>0.37</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25">
         <v>4.0199999999999996</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" hidden="1">
+      <c r="A26" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26">
         <v>0.17</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" hidden="1">
+      <c r="A27" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27">
         <v>143</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27">
         <v>89</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28">
         <v>7.75</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29">
         <v>6.66</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" hidden="1">
+      <c r="A30" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30">
         <v>127</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30">
         <v>61</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30">
         <v>0.56000000000000005</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
         <v>23</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31">
         <v>4.21</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" hidden="1">
+      <c r="A32" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32">
         <v>110</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32">
         <v>60</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32">
         <v>0.78</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33">
         <v>6.33</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" hidden="1">
+      <c r="A34" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34">
         <v>101</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34">
         <v>85</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="G34">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35">
         <v>5.37</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35">
         <v>0.37</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="G35">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" hidden="1">
+      <c r="A36" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36">
         <v>111</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36">
         <v>88</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="G36">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
         <v>27</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37">
         <v>4.3</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37">
         <v>0.64</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="G37">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" hidden="1">
+      <c r="A38" t="s">
         <v>27</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38">
         <v>133</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38">
         <v>84</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+      <c r="G38">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39">
         <v>6.94</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39">
         <v>0.28000000000000003</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="G39">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" hidden="1">
+      <c r="A40" t="s">
         <v>28</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40">
         <v>138</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40">
         <v>86</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
+      <c r="G40">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41">
         <v>5.86</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41">
         <v>0.32</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+      <c r="G41">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
         <v>30</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42">
         <v>4.49</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42">
         <v>0.67</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="G42">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" hidden="1">
+      <c r="A43" t="s">
         <v>30</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43">
         <v>131</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43">
         <v>87</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
+      <c r="G43">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" hidden="1">
+      <c r="A44" t="s">
         <v>117</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44">
         <v>91</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44">
         <v>79</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44">
         <v>0.41</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="G44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" hidden="1">
+      <c r="A45" t="s">
         <v>31</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45">
         <v>136</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45">
         <v>89</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="G45">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
         <v>32</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46">
         <v>4.6100000000000003</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46">
         <v>0.59</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="G46">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" hidden="1">
+      <c r="A47" t="s">
         <v>32</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47">
         <v>0.17</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47">
         <v>0.68</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="G47">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" hidden="1">
+      <c r="A48" t="s">
         <v>33</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48">
         <v>150</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48">
         <v>71</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+      <c r="G48">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
         <v>34</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49">
         <v>6.25</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49">
         <v>0.76</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="G49">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
         <v>35</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50">
         <v>5.58</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50">
         <v>0.46</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+      <c r="G50">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" hidden="1">
+      <c r="A51" t="s">
         <v>36</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51">
         <v>92</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51">
         <v>64</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51">
         <v>0.61</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
+      <c r="G51">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
         <v>37</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52">
         <v>4.37</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52">
         <v>0.52</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
+      <c r="G52">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" hidden="1">
+      <c r="A53" t="s">
         <v>37</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53">
         <v>140</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53">
         <v>66</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53">
         <v>0.53</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
+      <c r="G53">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
         <v>38</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54">
         <v>6.82</v>
       </c>
-      <c r="F54" s="3">
+      <c r="F54">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
+      <c r="G54">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" hidden="1">
+      <c r="A55" t="s">
         <v>38</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55">
         <v>110</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55">
         <v>68</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55">
         <v>0.44</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
+      <c r="G55">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
         <v>39</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56">
         <v>6.57</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
+      <c r="G56">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" hidden="1">
+      <c r="A57" t="s">
         <v>40</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57">
         <v>128</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57">
         <v>77</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57">
         <v>0.45</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
+      <c r="G57">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
         <v>41</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58">
         <v>4.2</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58">
         <v>0.62</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
+      <c r="G58">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" hidden="1">
+      <c r="A59" t="s">
         <v>41</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59">
         <v>93</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59">
         <v>84</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59">
         <v>0.61</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
+      <c r="G59">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
         <v>42</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60">
         <v>6.93</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
+      <c r="G60">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" hidden="1">
+      <c r="A61" t="s">
         <v>42</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61">
         <v>103</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61">
         <v>77</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
+      <c r="G61">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
         <v>43</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62">
         <v>6.18</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62">
         <v>0.76</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
+      <c r="G62">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
         <v>44</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D63">
         <v>4.25</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F63">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+      <c r="G63">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" hidden="1">
+      <c r="A64" t="s">
         <v>44</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64">
         <v>98</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64">
         <v>85</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F64">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+      <c r="G64">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" hidden="1">
+      <c r="A65" t="s">
         <v>118</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65">
         <v>118</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65">
         <v>90</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65">
         <v>0.62</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
+      <c r="G65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" hidden="1">
+      <c r="A66" t="s">
         <v>45</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66">
         <v>117</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66">
         <v>74</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F66">
         <v>0.53</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
+      <c r="G66">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
         <v>46</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67">
         <v>4.6100000000000003</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67">
         <v>0.42</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
+      <c r="G67">
+        <f t="shared" ref="G67:G130" si="1">HOUR(A67)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" hidden="1">
+      <c r="A68" t="s">
         <v>46</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E68">
         <v>0.17</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68">
         <v>0.64</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
+      <c r="G68">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" hidden="1">
+      <c r="A69" t="s">
         <v>47</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69">
         <v>106</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69">
         <v>71</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F69">
         <v>0.62</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+      <c r="G69">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
         <v>48</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70">
         <v>6.31</v>
       </c>
-      <c r="F70" s="3">
+      <c r="F70">
         <v>0.48</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
+      <c r="G70">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
         <v>49</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D71">
         <v>5.13</v>
       </c>
-      <c r="F71" s="3">
+      <c r="F71">
         <v>0.98</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
+      <c r="G71">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" hidden="1">
+      <c r="A72" t="s">
         <v>50</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72">
         <v>97</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72">
         <v>74</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72">
         <v>0.64</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
+      <c r="G72">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
         <v>51</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73">
         <v>4.95</v>
       </c>
-      <c r="F73" s="3">
+      <c r="F73">
         <v>0.63</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
+      <c r="G73">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" hidden="1">
+      <c r="A74" t="s">
         <v>51</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74">
         <v>124</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74">
         <v>73</v>
       </c>
-      <c r="F74" s="3">
+      <c r="F74">
         <v>0.49</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
+      <c r="G74">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
         <v>52</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D75">
         <v>7.74</v>
       </c>
-      <c r="F75" s="3">
+      <c r="F75">
         <v>0.69</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
+      <c r="G75">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" hidden="1">
+      <c r="A76" t="s">
         <v>52</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76">
         <v>106</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C76">
         <v>63</v>
       </c>
-      <c r="F76" s="3">
+      <c r="F76">
         <v>0.71</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
+      <c r="G76">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
         <v>53</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D77">
         <v>6.62</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F77">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
+      <c r="G77">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" hidden="1">
+      <c r="A78" t="s">
         <v>54</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78">
         <v>139</v>
       </c>
-      <c r="C78" s="3">
+      <c r="C78">
         <v>67</v>
       </c>
-      <c r="F78" s="3">
+      <c r="F78">
         <v>0.89</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
+      <c r="G78">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
         <v>55</v>
       </c>
-      <c r="D79" s="3">
+      <c r="D79">
         <v>4.3</v>
       </c>
-      <c r="F79" s="3">
+      <c r="F79">
         <v>0.22</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
+      <c r="G79">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" hidden="1">
+      <c r="A80" t="s">
         <v>55</v>
       </c>
-      <c r="B80" s="3">
+      <c r="B80">
         <v>93</v>
       </c>
-      <c r="C80" s="3">
+      <c r="C80">
         <v>61</v>
       </c>
-      <c r="F80" s="3">
+      <c r="F80">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
+      <c r="G80">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
         <v>56</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81">
         <v>6.18</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
+      <c r="G81">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" hidden="1">
+      <c r="A82" t="s">
         <v>56</v>
       </c>
-      <c r="B82" s="3">
+      <c r="B82">
         <v>95</v>
       </c>
-      <c r="C82" s="3">
+      <c r="C82">
         <v>81</v>
       </c>
-      <c r="F82" s="3">
+      <c r="F82">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
+      <c r="G82">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
         <v>57</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83">
         <v>6.37</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
+      <c r="G83">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
         <v>58</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D84">
         <v>4.6399999999999997</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F84">
         <v>0.63</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
+      <c r="G84">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" hidden="1">
+      <c r="A85" t="s">
         <v>58</v>
       </c>
-      <c r="B85" s="3">
+      <c r="B85">
         <v>131</v>
       </c>
-      <c r="C85" s="3">
+      <c r="C85">
         <v>63</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F85">
         <v>0.73</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
+      <c r="G85">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" hidden="1">
+      <c r="A86" t="s">
         <v>119</v>
       </c>
-      <c r="B86" s="3">
+      <c r="B86">
         <v>107</v>
       </c>
-      <c r="C86" s="3">
+      <c r="C86">
         <v>74</v>
       </c>
-      <c r="F86" s="3">
+      <c r="F86">
         <v>0.63</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
+      <c r="G86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" hidden="1">
+      <c r="A87" t="s">
         <v>59</v>
       </c>
-      <c r="B87" s="3">
+      <c r="B87">
         <v>107</v>
       </c>
-      <c r="C87" s="3">
+      <c r="C87">
         <v>85</v>
       </c>
-      <c r="F87" s="3">
+      <c r="F87">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
+      <c r="G87">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
         <v>60</v>
       </c>
-      <c r="D88" s="3">
+      <c r="D88">
         <v>4.12</v>
       </c>
-      <c r="F88" s="3">
+      <c r="F88">
         <v>0.78</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
+      <c r="G88">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" hidden="1">
+      <c r="A89" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89">
         <v>0.17</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89">
         <v>0.66</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
+      <c r="G89">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" hidden="1">
+      <c r="A90" t="s">
         <v>61</v>
       </c>
-      <c r="B90" s="3">
+      <c r="B90">
         <v>143</v>
       </c>
-      <c r="C90" s="3">
+      <c r="C90">
         <v>61</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F90">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
+      <c r="G90">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
         <v>62</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91">
         <v>6.89</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91">
         <v>0.39</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
+      <c r="G91">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
         <v>63</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D92">
         <v>5.07</v>
       </c>
-      <c r="F92" s="3">
+      <c r="F92">
         <v>0.69</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
+      <c r="G92">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" hidden="1">
+      <c r="A93" t="s">
         <v>64</v>
       </c>
-      <c r="B93" s="3">
+      <c r="B93">
         <v>99</v>
       </c>
-      <c r="C93" s="3">
+      <c r="C93">
         <v>89</v>
       </c>
-      <c r="F93" s="3">
+      <c r="F93">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
+      <c r="G93">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
         <v>65</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94">
         <v>4.91</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94">
         <v>0.74</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
+      <c r="G94">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" hidden="1">
+      <c r="A95" t="s">
         <v>65</v>
       </c>
-      <c r="B95" s="3">
+      <c r="B95">
         <v>125</v>
       </c>
-      <c r="C95" s="3">
+      <c r="C95">
         <v>73</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F95">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
+      <c r="G95">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
         <v>66</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96">
         <v>6.47</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
+      <c r="G96">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" hidden="1">
+      <c r="A97" t="s">
         <v>66</v>
       </c>
-      <c r="B97" s="3">
+      <c r="B97">
         <v>120</v>
       </c>
-      <c r="C97" s="3">
+      <c r="C97">
         <v>75</v>
       </c>
-      <c r="F97" s="3">
+      <c r="F97">
         <v>0.21</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
+      <c r="G97">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
         <v>67</v>
       </c>
-      <c r="D98" s="3">
+      <c r="D98">
         <v>6.33</v>
       </c>
-      <c r="F98" s="3">
+      <c r="F98">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
+      <c r="G98">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" hidden="1">
+      <c r="A99" t="s">
         <v>68</v>
       </c>
-      <c r="B99" s="3">
+      <c r="B99">
         <v>104</v>
       </c>
-      <c r="C99" s="3">
+      <c r="C99">
         <v>67</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F99">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
+      <c r="G99">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
         <v>69</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100">
         <v>4.3099999999999996</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100">
         <v>0.76</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
+      <c r="G100">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" hidden="1">
+      <c r="A101" t="s">
         <v>69</v>
       </c>
-      <c r="B101" s="3">
+      <c r="B101">
         <v>103</v>
       </c>
-      <c r="C101" s="3">
+      <c r="C101">
         <v>82</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101">
         <v>0.64</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
+      <c r="G101">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
         <v>70</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102">
         <v>6.94</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F102">
         <v>0.71</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
+      <c r="G102">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" hidden="1">
+      <c r="A103" t="s">
         <v>70</v>
       </c>
-      <c r="B103" s="3">
+      <c r="B103">
         <v>129</v>
       </c>
-      <c r="C103" s="3">
+      <c r="C103">
         <v>80</v>
       </c>
-      <c r="F103" s="3">
+      <c r="F103">
         <v>0.38</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
+      <c r="G103">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
         <v>71</v>
       </c>
-      <c r="D104" s="3">
+      <c r="D104">
         <v>6.09</v>
       </c>
-      <c r="F104" s="3">
+      <c r="F104">
         <v>0.93</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
+      <c r="G104">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
         <v>72</v>
       </c>
-      <c r="D105" s="3">
+      <c r="D105">
         <v>4.38</v>
       </c>
-      <c r="F105" s="3">
+      <c r="F105">
         <v>0.76</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="s">
+      <c r="G105">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" hidden="1">
+      <c r="A106" t="s">
         <v>72</v>
       </c>
-      <c r="B106" s="3">
+      <c r="B106">
         <v>105</v>
       </c>
-      <c r="C106" s="3">
+      <c r="C106">
         <v>72</v>
       </c>
-      <c r="F106" s="3">
+      <c r="F106">
         <v>0.49</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
+      <c r="G106">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" hidden="1">
+      <c r="A107" t="s">
         <v>120</v>
       </c>
-      <c r="B107" s="3">
+      <c r="B107">
         <v>100</v>
       </c>
-      <c r="C107" s="3">
+      <c r="C107">
         <v>78</v>
       </c>
-      <c r="F107" s="3">
+      <c r="F107">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
+      <c r="G107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" hidden="1">
+      <c r="A108" t="s">
         <v>73</v>
       </c>
-      <c r="B108" s="3">
+      <c r="B108">
         <v>113</v>
       </c>
-      <c r="C108" s="3">
+      <c r="C108">
         <v>85</v>
       </c>
-      <c r="F108" s="3">
+      <c r="F108">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="s">
+      <c r="G108">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
         <v>74</v>
       </c>
-      <c r="D109" s="3">
+      <c r="D109">
         <v>4.97</v>
       </c>
-      <c r="F109" s="3">
+      <c r="F109">
         <v>0.56999999999999995</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="s">
+      <c r="G109">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" hidden="1">
+      <c r="A110" t="s">
         <v>74</v>
       </c>
-      <c r="E110" s="3">
+      <c r="E110">
         <v>0.17</v>
       </c>
-      <c r="F110" s="3">
+      <c r="F110">
         <v>0.63</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
+      <c r="G110">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" hidden="1">
+      <c r="A111" t="s">
         <v>75</v>
       </c>
-      <c r="B111" s="3">
+      <c r="B111">
         <v>124</v>
       </c>
-      <c r="C111" s="3">
+      <c r="C111">
         <v>87</v>
       </c>
-      <c r="F111" s="3">
+      <c r="F111">
         <v>0.36</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="3" t="s">
+      <c r="G111">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" t="s">
         <v>76</v>
       </c>
-      <c r="D112" s="3">
+      <c r="D112">
         <v>7.4</v>
       </c>
-      <c r="F112" s="3">
+      <c r="F112">
         <v>0.59</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="3" t="s">
+      <c r="G112">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" t="s">
         <v>77</v>
       </c>
-      <c r="D113" s="3">
+      <c r="D113">
         <v>6.88</v>
       </c>
-      <c r="F113" s="3">
+      <c r="F113">
         <v>0.76</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="s">
+      <c r="G113">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" hidden="1">
+      <c r="A114" t="s">
         <v>78</v>
       </c>
-      <c r="B114" s="3">
+      <c r="B114">
         <v>134</v>
       </c>
-      <c r="C114" s="3">
+      <c r="C114">
         <v>68</v>
       </c>
-      <c r="F114" s="3">
+      <c r="F114">
         <v>0.23</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="3" t="s">
+      <c r="G114">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" t="s">
         <v>79</v>
       </c>
-      <c r="D115" s="3">
+      <c r="D115">
         <v>4.8899999999999997</v>
       </c>
-      <c r="F115" s="3">
+      <c r="F115">
         <v>0.76</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="3" t="s">
+      <c r="G115">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" hidden="1">
+      <c r="A116" t="s">
         <v>79</v>
       </c>
-      <c r="B116" s="3">
+      <c r="B116">
         <v>118</v>
       </c>
-      <c r="C116" s="3">
+      <c r="C116">
         <v>74</v>
       </c>
-      <c r="F116" s="3">
+      <c r="F116">
         <v>0.57999999999999996</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="s">
+      <c r="G116">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
         <v>80</v>
       </c>
-      <c r="D117" s="3">
+      <c r="D117">
         <v>7.08</v>
       </c>
-      <c r="F117" s="3">
+      <c r="F117">
         <v>0.48</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="s">
+      <c r="G117">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" hidden="1">
+      <c r="A118" t="s">
         <v>80</v>
       </c>
-      <c r="B118" s="3">
+      <c r="B118">
         <v>134</v>
       </c>
-      <c r="C118" s="3">
+      <c r="C118">
         <v>60</v>
       </c>
-      <c r="F118" s="3">
+      <c r="F118">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
+      <c r="G118">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
         <v>81</v>
       </c>
-      <c r="D119" s="3">
+      <c r="D119">
         <v>6.84</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F119">
         <v>0.63</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
+      <c r="G119">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" hidden="1">
+      <c r="A120" t="s">
         <v>82</v>
       </c>
-      <c r="B120" s="3">
+      <c r="B120">
         <v>114</v>
       </c>
-      <c r="C120" s="3">
+      <c r="C120">
         <v>66</v>
       </c>
-      <c r="F120" s="3">
+      <c r="F120">
         <v>0.98</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
+      <c r="G120">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
         <v>83</v>
       </c>
-      <c r="D121" s="3">
+      <c r="D121">
         <v>4.09</v>
       </c>
-      <c r="F121" s="3">
+      <c r="F121">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="s">
+      <c r="G121">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" hidden="1">
+      <c r="A122" t="s">
         <v>83</v>
       </c>
-      <c r="B122" s="3">
+      <c r="B122">
         <v>98</v>
       </c>
-      <c r="C122" s="3">
+      <c r="C122">
         <v>83</v>
       </c>
-      <c r="F122" s="3">
+      <c r="F122">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="s">
+      <c r="G122">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
         <v>84</v>
       </c>
-      <c r="D123" s="3">
+      <c r="D123">
         <v>6.35</v>
       </c>
-      <c r="F123" s="3">
+      <c r="F123">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="s">
+      <c r="G123">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" hidden="1">
+      <c r="A124" t="s">
         <v>84</v>
       </c>
-      <c r="B124" s="3">
+      <c r="B124">
         <v>90</v>
       </c>
-      <c r="C124" s="3">
+      <c r="C124">
         <v>71</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F124">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
+      <c r="G124">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
         <v>85</v>
       </c>
-      <c r="D125" s="3">
+      <c r="D125">
         <v>5.09</v>
       </c>
-      <c r="F125" s="3">
+      <c r="F125">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="s">
+      <c r="G125">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
         <v>86</v>
       </c>
-      <c r="D126" s="3">
+      <c r="D126">
         <v>4.53</v>
       </c>
-      <c r="F126" s="3">
+      <c r="F126">
         <v>0.39</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="s">
+      <c r="G126">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" hidden="1">
+      <c r="A127" t="s">
         <v>86</v>
       </c>
-      <c r="B127" s="3">
+      <c r="B127">
         <v>97</v>
       </c>
-      <c r="C127" s="3">
+      <c r="C127">
         <v>83</v>
       </c>
-      <c r="F127" s="3">
+      <c r="F127">
         <v>0.37</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" s="3" t="s">
+      <c r="G127">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" hidden="1">
+      <c r="A128" t="s">
         <v>121</v>
       </c>
-      <c r="B128" s="3">
+      <c r="B128">
         <v>137</v>
       </c>
-      <c r="C128" s="3">
+      <c r="C128">
         <v>82</v>
       </c>
-      <c r="F128" s="3">
+      <c r="F128">
         <v>0.63</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="3" t="s">
+      <c r="G128">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" hidden="1">
+      <c r="A129" t="s">
         <v>87</v>
       </c>
-      <c r="B129" s="3">
+      <c r="B129">
         <v>106</v>
       </c>
-      <c r="C129" s="3">
+      <c r="C129">
         <v>67</v>
       </c>
-      <c r="F129" s="3">
+      <c r="F129">
         <v>0.69</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="3" t="s">
+      <c r="G129">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
         <v>88</v>
       </c>
-      <c r="D130" s="3">
+      <c r="D130">
         <v>4.3899999999999997</v>
       </c>
-      <c r="F130" s="3">
+      <c r="F130">
         <v>0.78</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="3" t="s">
+      <c r="G130">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" hidden="1">
+      <c r="A131" t="s">
         <v>88</v>
       </c>
-      <c r="E131" s="3">
+      <c r="E131">
         <v>0.17</v>
       </c>
-      <c r="F131" s="3">
+      <c r="F131">
         <v>0.68</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="3" t="s">
+      <c r="G131">
+        <f t="shared" ref="G131:G169" si="2">HOUR(A131)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" hidden="1">
+      <c r="A132" t="s">
         <v>89</v>
       </c>
-      <c r="B132" s="3">
+      <c r="B132">
         <v>134</v>
       </c>
-      <c r="C132" s="3">
+      <c r="C132">
         <v>62</v>
       </c>
-      <c r="F132" s="3">
+      <c r="F132">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="3" t="s">
+      <c r="G132">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
         <v>90</v>
       </c>
-      <c r="D133" s="3">
+      <c r="D133">
         <v>6.49</v>
       </c>
-      <c r="F133" s="3">
+      <c r="F133">
         <v>0.32</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="3" t="s">
+      <c r="G133">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" t="s">
         <v>91</v>
       </c>
-      <c r="D134" s="3">
+      <c r="D134">
         <v>6.66</v>
       </c>
-      <c r="F134" s="3">
+      <c r="F134">
         <v>0.63</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="3" t="s">
+      <c r="G134">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" hidden="1">
+      <c r="A135" t="s">
         <v>92</v>
       </c>
-      <c r="B135" s="3">
+      <c r="B135">
         <v>122</v>
       </c>
-      <c r="C135" s="3">
+      <c r="C135">
         <v>86</v>
       </c>
-      <c r="F135" s="3">
+      <c r="F135">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="3" t="s">
+      <c r="G135">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" t="s">
         <v>93</v>
       </c>
-      <c r="D136" s="3">
+      <c r="D136">
         <v>4.3600000000000003</v>
       </c>
-      <c r="F136" s="3">
+      <c r="F136">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="3" t="s">
+      <c r="G136">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" hidden="1">
+      <c r="A137" t="s">
         <v>93</v>
       </c>
-      <c r="B137" s="3">
+      <c r="B137">
         <v>94</v>
       </c>
-      <c r="C137" s="3">
+      <c r="C137">
         <v>69</v>
       </c>
-      <c r="F137" s="3">
+      <c r="F137">
         <v>0.91</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="3" t="s">
+      <c r="G137">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" t="s">
         <v>94</v>
       </c>
-      <c r="D138" s="3">
+      <c r="D138">
         <v>6.51</v>
       </c>
-      <c r="F138" s="3">
+      <c r="F138">
         <v>0.57999999999999996</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="3" t="s">
+      <c r="G138">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" hidden="1">
+      <c r="A139" t="s">
         <v>94</v>
       </c>
-      <c r="B139" s="3">
+      <c r="B139">
         <v>128</v>
       </c>
-      <c r="C139" s="3">
+      <c r="C139">
         <v>85</v>
       </c>
-      <c r="F139" s="3">
+      <c r="F139">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="3" t="s">
+      <c r="G139">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" t="s">
         <v>95</v>
       </c>
-      <c r="D140" s="3">
+      <c r="D140">
         <v>6.09</v>
       </c>
-      <c r="F140" s="3">
+      <c r="F140">
         <v>0.57999999999999996</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="3" t="s">
+      <c r="G140">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" hidden="1">
+      <c r="A141" t="s">
         <v>96</v>
       </c>
-      <c r="B141" s="3">
+      <c r="B141">
         <v>130</v>
       </c>
-      <c r="C141" s="3">
+      <c r="C141">
         <v>87</v>
       </c>
-      <c r="F141" s="3">
+      <c r="F141">
         <v>0.89</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="s">
+      <c r="G141">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" t="s">
         <v>97</v>
       </c>
-      <c r="D142" s="3">
+      <c r="D142">
         <v>4.1399999999999997</v>
       </c>
-      <c r="F142" s="3">
+      <c r="F142">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="3" t="s">
+      <c r="G142">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" hidden="1">
+      <c r="A143" t="s">
         <v>97</v>
       </c>
-      <c r="B143" s="3">
+      <c r="B143">
         <v>96</v>
       </c>
-      <c r="C143" s="3">
+      <c r="C143">
         <v>68</v>
       </c>
-      <c r="F143" s="3">
+      <c r="F143">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="3" t="s">
+      <c r="G143">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" t="s">
         <v>98</v>
       </c>
-      <c r="D144" s="3">
+      <c r="D144">
         <v>7.44</v>
       </c>
-      <c r="F144" s="3">
+      <c r="F144">
         <v>0.47</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="3" t="s">
+      <c r="G144">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" hidden="1">
+      <c r="A145" t="s">
         <v>98</v>
       </c>
-      <c r="B145" s="3">
+      <c r="B145">
         <v>97</v>
       </c>
-      <c r="C145" s="3">
+      <c r="C145">
         <v>71</v>
       </c>
-      <c r="F145" s="3">
+      <c r="F145">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="3" t="s">
+      <c r="G145">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" t="s">
         <v>99</v>
       </c>
-      <c r="D146" s="3">
+      <c r="D146">
         <v>5.15</v>
       </c>
-      <c r="F146" s="3">
+      <c r="F146">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="3" t="s">
+      <c r="G146">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" t="s">
         <v>100</v>
       </c>
-      <c r="D147" s="3">
+      <c r="D147">
         <v>5.19</v>
       </c>
-      <c r="F147" s="3">
+      <c r="F147">
         <v>0.49</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="3" t="s">
+      <c r="G147">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" hidden="1">
+      <c r="A148" t="s">
         <v>100</v>
       </c>
-      <c r="B148" s="3">
+      <c r="B148">
         <v>123</v>
       </c>
-      <c r="C148" s="3">
+      <c r="C148">
         <v>60</v>
       </c>
-      <c r="F148" s="3">
+      <c r="F148">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="3" t="s">
+      <c r="G148">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" hidden="1">
+      <c r="A149" t="s">
         <v>122</v>
       </c>
-      <c r="B149" s="3">
+      <c r="B149">
         <v>115</v>
       </c>
-      <c r="C149" s="3">
+      <c r="C149">
         <v>82</v>
       </c>
-      <c r="F149" s="3">
+      <c r="F149">
         <v>0.69</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="3" t="s">
+      <c r="G149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" hidden="1">
+      <c r="A150" t="s">
         <v>101</v>
       </c>
-      <c r="B150" s="3">
+      <c r="B150">
         <v>112</v>
       </c>
-      <c r="C150" s="3">
+      <c r="C150">
         <v>89</v>
       </c>
-      <c r="F150" s="3">
+      <c r="F150">
         <v>0.46</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="3" t="s">
+      <c r="G150">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" t="s">
         <v>102</v>
       </c>
-      <c r="D151" s="3">
+      <c r="D151">
         <v>4.7699999999999996</v>
       </c>
-      <c r="F151" s="3">
+      <c r="F151">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="3" t="s">
+      <c r="G151">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" hidden="1">
+      <c r="A152" t="s">
         <v>102</v>
       </c>
-      <c r="E152" s="3">
+      <c r="E152">
         <v>0.17</v>
       </c>
-      <c r="F152" s="3">
+      <c r="F152">
         <v>0.66</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="3" t="s">
+      <c r="G152">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" hidden="1">
+      <c r="A153" t="s">
         <v>103</v>
       </c>
-      <c r="B153" s="3">
+      <c r="B153">
         <v>123</v>
       </c>
-      <c r="C153" s="3">
+      <c r="C153">
         <v>64</v>
       </c>
-      <c r="F153" s="3">
+      <c r="F153">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" s="3" t="s">
+      <c r="G153">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" t="s">
         <v>104</v>
       </c>
-      <c r="D154" s="3">
+      <c r="D154">
         <v>6.36</v>
       </c>
-      <c r="F154" s="3">
+      <c r="F154">
         <v>0.84</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="3" t="s">
+      <c r="G154">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" t="s">
         <v>105</v>
       </c>
-      <c r="D155" s="3">
+      <c r="D155">
         <v>5.01</v>
       </c>
-      <c r="F155" s="3">
+      <c r="F155">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" s="3" t="s">
+      <c r="G155">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" hidden="1">
+      <c r="A156" t="s">
         <v>106</v>
       </c>
-      <c r="B156" s="3">
+      <c r="B156">
         <v>124</v>
       </c>
-      <c r="C156" s="3">
+      <c r="C156">
         <v>71</v>
       </c>
-      <c r="F156" s="3">
+      <c r="F156">
         <v>0.54</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="3" t="s">
+      <c r="G156">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" t="s">
         <v>107</v>
       </c>
-      <c r="D157" s="3">
+      <c r="D157">
         <v>4.82</v>
       </c>
-      <c r="F157" s="3">
+      <c r="F157">
         <v>0.52</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="3" t="s">
+      <c r="G157">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" hidden="1">
+      <c r="A158" t="s">
         <v>107</v>
       </c>
-      <c r="B158" s="3">
+      <c r="B158">
         <v>129</v>
       </c>
-      <c r="C158" s="3">
+      <c r="C158">
         <v>81</v>
       </c>
-      <c r="F158" s="3">
+      <c r="F158">
         <v>0.93</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="3" t="s">
+      <c r="G158">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" t="s">
         <v>108</v>
       </c>
-      <c r="D159" s="3">
+      <c r="D159">
         <v>7.27</v>
       </c>
-      <c r="F159" s="3">
+      <c r="F159">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="3" t="s">
+      <c r="G159">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" hidden="1">
+      <c r="A160" t="s">
         <v>108</v>
       </c>
-      <c r="B160" s="3">
+      <c r="B160">
         <v>116</v>
       </c>
-      <c r="C160" s="3">
+      <c r="C160">
         <v>62</v>
       </c>
-      <c r="F160" s="3">
+      <c r="F160">
         <v>0.71</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="3" t="s">
+      <c r="G160">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
         <v>109</v>
       </c>
-      <c r="D161" s="3">
+      <c r="D161">
         <v>6.46</v>
       </c>
-      <c r="F161" s="3">
+      <c r="F161">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="3" t="s">
+      <c r="G161">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" hidden="1">
+      <c r="A162" t="s">
         <v>110</v>
       </c>
-      <c r="B162" s="3">
+      <c r="B162">
         <v>90</v>
       </c>
-      <c r="C162" s="3">
+      <c r="C162">
         <v>62</v>
       </c>
-      <c r="F162" s="3">
+      <c r="F162">
         <v>0.28999999999999998</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="3" t="s">
+      <c r="G162">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
         <v>111</v>
       </c>
-      <c r="D163" s="3">
+      <c r="D163">
         <v>4.7699999999999996</v>
       </c>
-      <c r="F163" s="3">
+      <c r="F163">
         <v>0.42</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="3" t="s">
+      <c r="G163">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" hidden="1">
+      <c r="A164" t="s">
         <v>111</v>
       </c>
-      <c r="B164" s="3">
+      <c r="B164">
         <v>126</v>
       </c>
-      <c r="C164" s="3">
+      <c r="C164">
         <v>74</v>
       </c>
-      <c r="F164" s="3">
+      <c r="F164">
         <v>0.34</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="3" t="s">
+      <c r="G164">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
         <v>112</v>
       </c>
-      <c r="D165" s="3">
+      <c r="D165">
         <v>6.13</v>
       </c>
-      <c r="F165" s="3">
+      <c r="F165">
         <v>0.54</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" s="3" t="s">
+      <c r="G165">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" hidden="1">
+      <c r="A166" t="s">
         <v>112</v>
       </c>
-      <c r="B166" s="3">
+      <c r="B166">
         <v>103</v>
       </c>
-      <c r="C166" s="3">
+      <c r="C166">
         <v>62</v>
       </c>
-      <c r="F166" s="3">
+      <c r="F166">
         <v>0.69</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="3" t="s">
+      <c r="G166">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
         <v>113</v>
       </c>
-      <c r="D167" s="3">
+      <c r="D167">
         <v>5.72</v>
       </c>
-      <c r="F167" s="3">
+      <c r="F167">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="3" t="s">
+      <c r="G167">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
         <v>114</v>
       </c>
-      <c r="D168" s="3">
+      <c r="D168">
         <v>4.32</v>
       </c>
-      <c r="F168" s="3">
+      <c r="F168">
         <v>0.46</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" s="3" t="s">
+      <c r="G168">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" hidden="1">
+      <c r="A169" t="s">
         <v>114</v>
       </c>
-      <c r="B169" s="3">
+      <c r="B169">
         <v>90</v>
       </c>
-      <c r="C169" s="3">
+      <c r="C169">
         <v>64</v>
       </c>
-      <c r="F169" s="3">
+      <c r="F169">
         <v>0.6</v>
       </c>
+      <c r="G169">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
-  <sortState ref="A2:E161">
+  <autoFilter ref="A1:G169" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E161">
     <sortCondition ref="A2:A161"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
